--- a/downloads/annee-creation-decennies.xlsx
+++ b/downloads/annee-creation-decennies.xlsx
@@ -431,7 +431,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,10 +492,10 @@
         <v>1889</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -576,10 +576,10 @@
         <v>1949</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11">
@@ -618,10 +618,10 @@
         <v>1979</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="14">
@@ -632,10 +632,10 @@
         <v>1989</v>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -646,10 +646,10 @@
         <v>1999</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -660,10 +660,10 @@
         <v>2009</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="17">
@@ -688,10 +688,10 @@
         <v>2026</v>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>2.142857142857143</v>
+        <v>2.428571428571428</v>
       </c>
     </row>
   </sheetData>
